--- a/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones_Video_466_EXP5_FAPS4_40V.xlsx
+++ b/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones_Video_466_EXP5_FAPS4_40V.xlsx
@@ -24,16 +24,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,22 +424,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -794,312 +782,312 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1346,52 +1334,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -1446,87 +1434,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>busqueda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>veredicto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>clasificacion</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>periodo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>periodo_err_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>jitter_ms</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>p_valor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>n_eventos_tren</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>n_ranuras</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>captura_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_dudosos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>n_sacados_tiempo_amplitud</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inicio_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>fin_s</t>
         </is>
@@ -1606,32 +1594,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -1752,27 +1740,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>junto_al_borde</t>
         </is>
@@ -1878,117 +1866,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
@@ -2374,112 +2362,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>

--- a/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones_Video_466_EXP5_FAPS4_40V.xlsx
+++ b/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones_Video_466_EXP5_FAPS4_40V.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_466_EXP5_FAPS4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_466_EXP5_FAP" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ritmo_Video_466_EXP5_FAPS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="trenes_Video_466_EXP5_FAP" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="grilla_Video_466_EXP5_FAP" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="eventos_Video_466_EXP5_FAP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="cinetica_Video_466_EXP5_FAP" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="cin_grupos_Video_466_EXP5_F" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_466_EXP5_FAPS4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_466_EXP5_FAP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_466_EXP5_FAPS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trenes_Video_466_EXP5_FAP" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_466_EXP5_FAP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_466_EXP5_FAP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="basal_Video_466_EXP5_FAPS4" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_466_EXP5_FAP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cin_grupos_Video_466_EXP5_F" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -778,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ2"/>
+  <dimension ref="A1:BW2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,162 +935,227 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>basal_n_contracciones</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>basal_instantes_s</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>basal_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
         </is>
       </c>
     </row>
@@ -1212,111 +1278,158 @@
           <t>2.127-2.3</t>
         </is>
       </c>
-      <c r="AE2" t="n">
-        <v>5</v>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>1.925-2.321</t>
+        </is>
       </c>
       <c r="AF2" t="n">
-        <v>5</v>
+        <v>4.358199999999954</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH2" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.2549890109890072</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.2543-0.2852</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>1</v>
       </c>
       <c r="AK2" t="n">
+        <v>0.1833399634202131</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.1543-0.255</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.1518-0.2921</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
         <v>0.1366666666666596</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AO2" t="n">
         <v>0.3649999999999984</v>
       </c>
-      <c r="AM2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP2" t="b">
-        <v>1</v>
+      <c r="AP2" t="n">
+        <v>5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.1920369393139794</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.175-0.1952</t>
-        </is>
-      </c>
-      <c r="AS2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.2264475189478592</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.2066-0.2455</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.158-0.292</t>
+        </is>
+      </c>
+      <c r="AW2" t="n">
         <v>0.03333333333333854</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AX2" t="n">
         <v>0.259999999999998</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>RT50: mediana sobre los 3 de 5 eventos medibles</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>RT50: mediana sobre los 4 de 5 eventos medibles</t>
+        </is>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
         <v>2</v>
       </c>
-      <c r="BB2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG2" t="n">
         <v>0.5666666666666345</v>
       </c>
-      <c r="BD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="inlineStr">
         <is>
           <t>1.5 s: 5 | 2 s: 5 | 3 s: 5</t>
         </is>
       </c>
-      <c r="BF2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BJ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BK2" t="inlineStr">
         <is>
           <t>5 ev en k=6.431-20.182</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>0.3023021400000065</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BM2" t="n">
         <v>0.1772448300000057</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BN2" t="n">
         <v>1.705562526139673</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>0-10 s</t>
+        </is>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.4135800000000127</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.205885935542942</v>
+      </c>
+      <c r="BS2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0 contraccion(es) en 10.0 s; actividad basal 0.21 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1765,6 +1878,16 @@
           <t>junto_al_borde</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>en_promedio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>reportable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1781,6 +1904,12 @@
       </c>
       <c r="E2" t="b">
         <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1799,6 +1928,12 @@
       <c r="E3" t="b">
         <v>0</v>
       </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1816,6 +1951,12 @@
       <c r="E4" t="b">
         <v>0</v>
       </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1833,6 +1974,12 @@
       <c r="E5" t="b">
         <v>0</v>
       </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1849,6 +1996,12 @@
       </c>
       <c r="E6" t="b">
         <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1862,489 +2015,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>dato</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tren</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>frame_pico</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>tiempo_s</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>amplitud_px</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>grosor_reposo_px</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>amplitud_relativa_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>meseta_pico_frames</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>onset_s</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ttp_frames</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ttp_s</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ttp_min_s</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ttp_max_s</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ttp_medible</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>rt50_frames</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>rt50_s</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>rt50_min_s</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>rt50_max_s</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>rt50_medible</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>offset_s</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>duracion_frames</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>duracion_s</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>420</v>
-      </c>
-      <c r="E2" t="n">
-        <v>14.24333333333333</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3.873699999999985</v>
-      </c>
-      <c r="G2" t="n">
-        <v>201.2478806612662</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.924840146028702</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14.02832670324646</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.215006630086874</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.1366666666666596</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.3766666666666705</v>
-      </c>
-      <c r="O2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.1983675000987493</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.02500000000000036</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.2700000000000014</v>
-      </c>
-      <c r="T2" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>14.6315440736754</v>
-      </c>
-      <c r="V2" t="n">
-        <v>19</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.6032173704289399</v>
+          <t>10.0</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>706</v>
-      </c>
-      <c r="E3" t="n">
-        <v>24.32</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4.669500000000028</v>
-      </c>
-      <c r="G3" t="n">
-        <v>201.1517691000597</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.321381522464891</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>24.02785434243768</v>
-      </c>
-      <c r="K3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.2921456575623189</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.1733333333333285</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.3649999999999984</v>
-      </c>
-      <c r="O3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.1195689730485334</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.04500000000000171</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.2300000000000004</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>24.64548552960188</v>
-      </c>
-      <c r="V3" t="n">
-        <v>20</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.6176311871641964</v>
+          <t>0-10 s</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>999</v>
-      </c>
-      <c r="E4" t="n">
-        <v>34.27666666666667</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4.358199999999954</v>
-      </c>
-      <c r="G4" t="n">
-        <v>201.3626054338658</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.164354196058181</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>34.02167765567766</v>
-      </c>
-      <c r="K4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.2549890109890072</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.2050000000000054</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.36666666666666</v>
-      </c>
-      <c r="O4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.1580046645138182</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.03333333333333854</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.2066666666666706</v>
-      </c>
-      <c r="T4" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>34.58778023249697</v>
-      </c>
-      <c r="V4" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.5661025768193113</v>
+          <t>0.4135800000000127</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1278</v>
-      </c>
-      <c r="E5" t="n">
-        <v>44.34333333333333</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4.285599999999988</v>
-      </c>
-      <c r="G5" t="n">
-        <v>201.4700163691977</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.127165161959655</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>44.05817923850575</v>
-      </c>
-      <c r="K5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.2851540948275755</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.1033333333333317</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.3433333333333337</v>
-      </c>
-      <c r="O5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.08952753779698241</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.02333333333334053</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.259999999999998</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>44.61379346241932</v>
-      </c>
-      <c r="V5" t="n">
-        <v>18</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.5556142239135653</v>
+          <t>0.20588593554294202</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1561</v>
-      </c>
-      <c r="E6" t="n">
-        <v>54.27666666666667</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.631599999999992</v>
-      </c>
-      <c r="G6" t="n">
-        <v>201.3795777713069</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.299935301910199</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>54.02236536266862</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.2543013039980551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.3616666666666717</v>
-      </c>
-      <c r="O6" t="b">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.1920369393139794</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.07000000000000028</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3333333333333286</v>
-      </c>
-      <c r="T6" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>54.67446774193549</v>
-      </c>
-      <c r="V6" t="n">
-        <v>20</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.6521023792668714</v>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>basal_n_contracciones</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>basal_instantes_s</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>basal_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0 contraccion(es) en 10.0 s; actividad basal 0.21 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2358,15 +2145,571 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>grupo</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>frame_llega_max</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tiempo_llega_max_s</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pico_dudoso_por_ruido</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>420</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14.24333333333333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.873699999999985</v>
+      </c>
+      <c r="G2" t="n">
+        <v>201.2478806612662</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.924840146028702</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>419</v>
+      </c>
+      <c r="K2" t="n">
+        <v>14.21166666666667</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>14.02832670324646</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1833399634202131</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1366666666666596</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3766666666666705</v>
+      </c>
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.2300341667654102</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.02500000000000036</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.2700000000000014</v>
+      </c>
+      <c r="W2" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>14.6315440736754</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.6032173704289399</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>706</v>
+      </c>
+      <c r="E3" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.669500000000028</v>
+      </c>
+      <c r="G3" t="n">
+        <v>201.1517691000597</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.321381522464891</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>706</v>
+      </c>
+      <c r="K3" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>24.02785434243768</v>
+      </c>
+      <c r="N3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2921456575623189</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1733333333333285</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.3649999999999984</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1195689730485334</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.04500000000000171</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2300000000000004</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>24.64548552960188</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.6176311871641964</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>34.27666666666667</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.358199999999954</v>
+      </c>
+      <c r="G4" t="n">
+        <v>201.3626054338658</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.164354196058181</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>34.27666666666667</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>34.02167765567766</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.2549890109890072</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2050000000000054</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.36666666666666</v>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1580046645138182</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.03333333333333854</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2066666666666706</v>
+      </c>
+      <c r="W4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>34.58778023249697</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.5661025768193113</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1278</v>
+      </c>
+      <c r="E5" t="n">
+        <v>44.34333333333333</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.285599999999988</v>
+      </c>
+      <c r="G5" t="n">
+        <v>201.4700163691977</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.127165161959655</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1274</v>
+      </c>
+      <c r="K5" t="n">
+        <v>44.21</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>44.05817923850575</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1518207614942497</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1033333333333317</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3433333333333337</v>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.2228608711303082</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.02333333333334053</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.259999999999998</v>
+      </c>
+      <c r="W5" t="b">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>44.61379346241932</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.5556142239135653</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1561</v>
+      </c>
+      <c r="E6" t="n">
+        <v>54.27666666666667</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.631599999999992</v>
+      </c>
+      <c r="G6" t="n">
+        <v>201.3795777713069</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.299935301910199</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1558</v>
+      </c>
+      <c r="K6" t="n">
+        <v>54.17666666666667</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>54.02236536266862</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1543013039980536</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3616666666666717</v>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.2920369393139808</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3333333333333286</v>
+      </c>
+      <c r="W6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>54.67446774193549</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.6521023792668714</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
@@ -2389,85 +2732,105 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
@@ -2493,61 +2856,79 @@
           <t>2.127-2.3</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>5</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1.925-2.321</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4.358199999999954</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I2" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2549890109890072</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.2543-0.2852</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
       </c>
       <c r="L2" t="n">
+        <v>0.1833399634202131</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.1543-0.255</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.1518-0.2921</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>0.1366666666666596</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>0.3649999999999984</v>
       </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
+      <c r="Q2" t="n">
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1920369393139794</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.175-0.1952</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.2264475189478592</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.2066-0.2455</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.158-0.292</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
         <v>0.03333333333333854</v>
       </c>
-      <c r="U2" t="n">
+      <c r="Y2" t="n">
         <v>0.259999999999998</v>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>RT50: mediana sobre los 3 de 5 eventos medibles</t>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>RT50: mediana sobre los 4 de 5 eventos medibles</t>
         </is>
       </c>
     </row>
@@ -2571,61 +2952,79 @@
           <t>2.127-2.3</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>5</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.925-2.321</t>
+        </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>4.358199999999954</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2549890109890072</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.2543-0.2852</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
       </c>
       <c r="L3" t="n">
+        <v>0.1833399634202131</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.1543-0.255</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.1518-0.2921</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>0.1366666666666596</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
         <v>0.3649999999999984</v>
       </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
+      <c r="Q3" t="n">
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1920369393139794</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.175-0.1952</t>
-        </is>
-      </c>
-      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.2264475189478592</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.2066-0.2455</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.158-0.292</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
         <v>0.03333333333333854</v>
       </c>
-      <c r="U3" t="n">
+      <c r="Y3" t="n">
         <v>0.259999999999998</v>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RT50: mediana sobre los 3 de 5 eventos medibles</t>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>RT50: mediana sobre los 4 de 5 eventos medibles</t>
         </is>
       </c>
     </row>
